--- a/embeds/data/energy-environment/slot-1-한국의-연평균-기온과-극한기후-발생-일수,-1981-2024.xlsx
+++ b/embeds/data/energy-environment/slot-1-한국의-연평균-기온과-극한기후-발생-일수,-1981-2024.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,7 +484,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -737,7 +737,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -967,7 +967,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1220,7 +1220,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1404,7 +1404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>연평균 기온(℃)</t>
+          <t>연평균 기온</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1496,7 +1496,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1680,7 +1680,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1749,7 +1749,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1818,7 +1818,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1933,7 +1933,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1956,7 +1956,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2002,7 +2002,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2186,7 +2186,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2278,7 +2278,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2324,7 +2324,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2393,7 +2393,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>폭염 일수(일)</t>
+          <t>폭염 일수</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2508,7 +2508,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2738,7 +2738,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2784,7 +2784,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2968,7 +2968,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3060,7 +3060,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3129,7 +3129,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3175,7 +3175,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3244,7 +3244,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3267,7 +3267,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3290,7 +3290,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3382,7 +3382,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3474,7 +3474,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한파 일수(일)</t>
+          <t>한파 일수</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3520,7 +3520,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3543,7 +3543,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3658,7 +3658,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3704,7 +3704,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3750,7 +3750,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3773,7 +3773,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3980,7 +3980,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4026,7 +4026,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4049,7 +4049,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4095,7 +4095,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4164,7 +4164,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4210,7 +4210,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4256,7 +4256,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4440,7 +4440,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>폭우 일수(일)</t>
+          <t>폭우 일수</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
